--- a/intermediate_data/LR_ANOVA.xlsx
+++ b/intermediate_data/LR_ANOVA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,12 +441,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>LR: Drug Targets Only</t>
+          <t>LR: Drug Targets with ATC Level 2</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>LR: Drug Targets with ATC</t>
+          <t>LR: Drug Targets with ATC Level 4</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -470,19 +470,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6867796610169493</v>
+        <v>0.6773898305084747</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6814576271186441</v>
+        <v>0.6999322033898306</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6999322033898306</v>
+        <v>0.6918983050847458</v>
       </c>
       <c r="F2" t="n">
-        <v>19.3565462147366</v>
+        <v>24.05550544701612</v>
       </c>
       <c r="G2" t="n">
-        <v>2.098206385434795e-08</v>
+        <v>4.445088917061744e-10</v>
       </c>
     </row>
     <row r="3">
@@ -495,19 +495,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.690179640718563</v>
+        <v>0.6823353293413171</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6548502994011975</v>
+        <v>0.6932035928143711</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6932035928143711</v>
+        <v>0.6886526946107786</v>
       </c>
       <c r="F3" t="n">
-        <v>106.7939958276595</v>
+        <v>6.104641691040935</v>
       </c>
       <c r="G3" t="n">
-        <v>3.45181082153424e-32</v>
+        <v>0.002674955490051547</v>
       </c>
     </row>
     <row r="4">
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6631012658227847</v>
+        <v>0.6660126582278481</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6776265822784809</v>
+        <v>0.696582278481013</v>
       </c>
       <c r="E4" t="n">
-        <v>0.696582278481013</v>
+        <v>0.6833860759493672</v>
       </c>
       <c r="F4" t="n">
-        <v>61.30777873196748</v>
+        <v>40.30932245283093</v>
       </c>
       <c r="G4" t="n">
-        <v>1.893996691768984e-21</v>
+        <v>2.059901464803533e-15</v>
       </c>
     </row>
     <row r="5">
@@ -545,19 +545,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6722516556291389</v>
+        <v>0.659503311258278</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6524834437086092</v>
+        <v>0.68182119205298</v>
       </c>
       <c r="E5" t="n">
-        <v>0.68182119205298</v>
+        <v>0.6803311258278144</v>
       </c>
       <c r="F5" t="n">
-        <v>56.68106927216688</v>
+        <v>33.81728011136875</v>
       </c>
       <c r="G5" t="n">
-        <v>3.439849872879137e-20</v>
+        <v>2.321029256549275e-13</v>
       </c>
     </row>
     <row r="6">
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7092434210526316</v>
+        <v>0.6980592105263157</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6963157894736841</v>
+        <v>0.7282894736842108</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7282894736842108</v>
+        <v>0.722828947368421</v>
       </c>
       <c r="F6" t="n">
-        <v>56.57601490921166</v>
+        <v>62.59065209197136</v>
       </c>
       <c r="G6" t="n">
-        <v>3.677584216653367e-20</v>
+        <v>8.603539280210223e-22</v>
       </c>
     </row>
     <row r="7">
@@ -595,19 +595,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7049063670411987</v>
+        <v>0.7041947565543072</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6479026217228465</v>
+        <v>0.711610486891386</v>
       </c>
       <c r="E7" t="n">
-        <v>0.711610486891386</v>
+        <v>0.6914606741573036</v>
       </c>
       <c r="F7" t="n">
-        <v>275.9093240695551</v>
+        <v>23.10932179878435</v>
       </c>
       <c r="G7" t="n">
-        <v>5.612887686341599e-58</v>
+        <v>9.544455748267532e-10</v>
       </c>
     </row>
     <row r="8">
@@ -620,19 +620,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6992028985507247</v>
+        <v>0.6954347826086957</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6816666666666669</v>
+        <v>0.7215942028985508</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7215942028985508</v>
+        <v>0.7120652173913044</v>
       </c>
       <c r="F8" t="n">
-        <v>73.66337589870152</v>
+        <v>43.01411599324474</v>
       </c>
       <c r="G8" t="n">
-        <v>1.216358792065034e-24</v>
+        <v>3.069476438721839e-16</v>
       </c>
     </row>
     <row r="9">
@@ -645,19 +645,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.7032089552238807</v>
+        <v>0.6971641791044776</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6552238805970149</v>
+        <v>0.6890298507462685</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6890298507462685</v>
+        <v>0.6815671641791043</v>
       </c>
       <c r="F9" t="n">
-        <v>101.6335137474286</v>
+        <v>9.161253260464571</v>
       </c>
       <c r="G9" t="n">
-        <v>4.265204227971962e-31</v>
+        <v>0.000156597526452931</v>
       </c>
     </row>
     <row r="10">
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6831199999999999</v>
+        <v>0.67804</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6759599999999999</v>
+        <v>0.69088</v>
       </c>
       <c r="E10" t="n">
-        <v>0.69088</v>
+        <v>0.7108800000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>10.41298432294274</v>
+        <v>46.39333983660303</v>
       </c>
       <c r="G10" t="n">
-        <v>5.012642570726757e-05</v>
+        <v>2.992109561217374e-17</v>
       </c>
     </row>
     <row r="11">
@@ -695,19 +695,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6854468085106382</v>
+        <v>0.6914042553191488</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6737446808510638</v>
+        <v>0.707191489361702</v>
       </c>
       <c r="E11" t="n">
-        <v>0.707191489361702</v>
+        <v>0.7027659574468085</v>
       </c>
       <c r="F11" t="n">
-        <v>47.15415322311037</v>
+        <v>11.33978401358586</v>
       </c>
       <c r="G11" t="n">
-        <v>1.784757914334441e-17</v>
+        <v>2.174720478586296e-05</v>
       </c>
     </row>
     <row r="12">
@@ -720,19 +720,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6725877192982456</v>
+        <v>0.6808771929824563</v>
       </c>
       <c r="D12" t="n">
-        <v>0.690219298245614</v>
+        <v>0.7053508771929825</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7053508771929825</v>
+        <v>0.7116666666666669</v>
       </c>
       <c r="F12" t="n">
-        <v>36.24663379554889</v>
+        <v>37.17989743664452</v>
       </c>
       <c r="G12" t="n">
-        <v>3.858018184649446e-14</v>
+        <v>1.952976387108713e-14</v>
       </c>
     </row>
     <row r="13">
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.7058482142857142</v>
+        <v>0.7125</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6795089285714284</v>
+        <v>0.7110267857142858</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7110267857142858</v>
+        <v>0.7047767857142859</v>
       </c>
       <c r="F13" t="n">
-        <v>39.65112276034737</v>
+        <v>2.077792271440818</v>
       </c>
       <c r="G13" t="n">
-        <v>3.292066374235704e-15</v>
+        <v>0.1279278962804363</v>
       </c>
     </row>
     <row r="14">
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6765573770491803</v>
+        <v>0.6717704918032789</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6602950819672131</v>
+        <v>0.696622950819672</v>
       </c>
       <c r="E14" t="n">
-        <v>0.696622950819672</v>
+        <v>0.6947540983606557</v>
       </c>
       <c r="F14" t="n">
-        <v>81.9785589092355</v>
+        <v>46.75478823632297</v>
       </c>
       <c r="G14" t="n">
-        <v>1.155576816982485e-26</v>
+        <v>2.340043953828122e-17</v>
       </c>
     </row>
     <row r="15">
@@ -795,19 +795,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6596601941747575</v>
+        <v>0.6583009708737864</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6553398058252428</v>
+        <v>0.6787864077669904</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6787864077669904</v>
+        <v>0.6751456310679613</v>
       </c>
       <c r="F15" t="n">
-        <v>23.75574795085676</v>
+        <v>13.56396186480767</v>
       </c>
       <c r="G15" t="n">
-        <v>5.659035544177698e-10</v>
+        <v>3.015411581737774e-06</v>
       </c>
     </row>
     <row r="16">
@@ -820,19 +820,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.6443378995433789</v>
+        <v>0.6375342465753424</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6527397260273972</v>
+        <v>0.6640182648401826</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6640182648401826</v>
+        <v>0.6708219178082192</v>
       </c>
       <c r="F16" t="n">
-        <v>15.53476733613888</v>
+        <v>52.72009826739698</v>
       </c>
       <c r="G16" t="n">
-        <v>5.408636673936809e-07</v>
+        <v>4.411800327838805e-19</v>
       </c>
     </row>
     <row r="17">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.7005022831050227</v>
+        <v>0.7016438356164382</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6868036529680366</v>
+        <v>0.7345662100456619</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7345662100456619</v>
+        <v>0.714337899543379</v>
       </c>
       <c r="F17" t="n">
-        <v>85.78520167585314</v>
+        <v>38.72166201774176</v>
       </c>
       <c r="G17" t="n">
-        <v>1.47174519440235e-27</v>
+        <v>6.407092729419809e-15</v>
       </c>
     </row>
     <row r="18">
@@ -870,19 +870,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.6588516746411485</v>
+        <v>0.6566507177033495</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6798086124401916</v>
+        <v>0.6929665071770339</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6929665071770339</v>
+        <v>0.6992344497607658</v>
       </c>
       <c r="F18" t="n">
-        <v>47.52491520033262</v>
+        <v>82.04361059499004</v>
       </c>
       <c r="G18" t="n">
-        <v>1.388826110444178e-17</v>
+        <v>1.115185824942769e-26</v>
       </c>
     </row>
     <row r="19">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.7077674418604651</v>
+        <v>0.7011162790697675</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6995813953488371</v>
+        <v>0.7373023255813953</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7373023255813953</v>
+        <v>0.7247441860465119</v>
       </c>
       <c r="F19" t="n">
-        <v>71.22741319304886</v>
+        <v>73.85824477748965</v>
       </c>
       <c r="G19" t="n">
-        <v>4.965509383323079e-24</v>
+        <v>1.087838645150714e-24</v>
       </c>
     </row>
     <row r="20">
@@ -920,19 +920,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.7028078817733991</v>
+        <v>0.6969950738916255</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6613793103448274</v>
+        <v>0.6925615763546797</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6925615763546797</v>
+        <v>0.6903940886699506</v>
       </c>
       <c r="F20" t="n">
-        <v>69.40355968885015</v>
+        <v>1.74201286390313</v>
       </c>
       <c r="G20" t="n">
-        <v>1.442476681745978e-23</v>
+        <v>0.1778412455309188</v>
       </c>
     </row>
     <row r="21">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.7080729166666667</v>
+        <v>0.7075520833333333</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6781770833333333</v>
+        <v>0.7122916666666668</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7122916666666668</v>
+        <v>0.7119791666666667</v>
       </c>
       <c r="F21" t="n">
-        <v>46.92358274199604</v>
+        <v>1.05081071778335</v>
       </c>
       <c r="G21" t="n">
-        <v>2.086706409476403e-17</v>
+        <v>0.3515957907756278</v>
       </c>
     </row>
     <row r="22">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.6791262135922329</v>
+        <v>0.6848058252427187</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6793203883495147</v>
+        <v>0.7035922330097086</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7035922330097086</v>
+        <v>0.7</v>
       </c>
       <c r="F22" t="n">
-        <v>26.77327220984593</v>
+        <v>14.84390917499315</v>
       </c>
       <c r="G22" t="n">
-        <v>5.1125389104095e-11</v>
+        <v>9.844962145822846e-07</v>
       </c>
     </row>
     <row r="23">
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.6069411764705882</v>
+        <v>0.6078235294117647</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6911764705882354</v>
+        <v>0.6864705882352942</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6864705882352942</v>
+        <v>0.673764705882353</v>
       </c>
       <c r="F23" t="n">
-        <v>250.1234801700232</v>
+        <v>207.0709166873064</v>
       </c>
       <c r="G23" t="n">
-        <v>6.50066090133675e-55</v>
+        <v>2.961419312398748e-49</v>
       </c>
     </row>
     <row r="24">
@@ -1020,19 +1020,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.6649489795918367</v>
+        <v>0.6587244897959184</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6609693877551019</v>
+        <v>0.6916326530612245</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6916326530612245</v>
+        <v>0.6882142857142859</v>
       </c>
       <c r="F24" t="n">
-        <v>41.94180430071413</v>
+        <v>41.39705153823402</v>
       </c>
       <c r="G24" t="n">
-        <v>6.500419729596046e-16</v>
+        <v>9.537696974516836e-16</v>
       </c>
     </row>
     <row r="25">
@@ -1045,19 +1045,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.7418446601941747</v>
+        <v>0.7371844660194175</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6990291262135924</v>
+        <v>0.7284466019417474</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7284466019417474</v>
+        <v>0.741116504854369</v>
       </c>
       <c r="F25" t="n">
-        <v>71.04696027414641</v>
+        <v>5.913433122219979</v>
       </c>
       <c r="G25" t="n">
-        <v>5.515258092734879e-24</v>
+        <v>0.003203358017333064</v>
       </c>
     </row>
     <row r="26">
@@ -1070,19 +1070,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.6063829787234043</v>
+        <v>0.611436170212766</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6162234042553192</v>
+        <v>0.6503191489361702</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6503191489361702</v>
+        <v>0.6616489361702128</v>
       </c>
       <c r="F26" t="n">
-        <v>68.98848819830172</v>
+        <v>82.79576900202082</v>
       </c>
       <c r="G26" t="n">
-        <v>1.841669162579787e-23</v>
+        <v>7.397600694628925e-27</v>
       </c>
     </row>
     <row r="27">
@@ -1095,19 +1095,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.7290810810810811</v>
+        <v>0.7111351351351352</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6843783783783784</v>
+        <v>0.7368108108108109</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7368108108108109</v>
+        <v>0.7112432432432432</v>
       </c>
       <c r="F27" t="n">
-        <v>111.3405376363197</v>
+        <v>25.58983388574368</v>
       </c>
       <c r="G27" t="n">
-        <v>3.967430059583093e-33</v>
+        <v>1.303485465575124e-10</v>
       </c>
     </row>
     <row r="28">
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.6710795454545453</v>
+        <v>0.6648863636363636</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6589772727272727</v>
+        <v>0.6646590909090909</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6646590909090909</v>
+        <v>0.6664772727272726</v>
       </c>
       <c r="F28" t="n">
-        <v>5.361094907102062</v>
+        <v>0.1589890964415606</v>
       </c>
       <c r="G28" t="n">
-        <v>0.005402069977236227</v>
+        <v>0.8531144485785489</v>
       </c>
     </row>
     <row r="29">
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.6544767441860466</v>
+        <v>0.6493023255813953</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6763953488372093</v>
+        <v>0.6994186046511629</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6994186046511629</v>
+        <v>0.6868023255813952</v>
       </c>
       <c r="F29" t="n">
-        <v>70.09644063860941</v>
+        <v>90.83053941681462</v>
       </c>
       <c r="G29" t="n">
-        <v>9.606653383649915e-24</v>
+        <v>1.022450202318627e-28</v>
       </c>
     </row>
     <row r="30">
@@ -1170,19 +1170,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.6416384180790961</v>
+        <v>0.6387570621468927</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6168361581920905</v>
+        <v>0.6570056497175142</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6570056497175142</v>
+        <v>0.674180790960452</v>
       </c>
       <c r="F30" t="n">
-        <v>57.27589389664455</v>
+        <v>43.15111510456465</v>
       </c>
       <c r="G30" t="n">
-        <v>2.358180710912796e-20</v>
+        <v>2.790020855737775e-16</v>
       </c>
     </row>
     <row r="31">
@@ -1195,19 +1195,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.6932512315270936</v>
+        <v>0.6882758620689655</v>
       </c>
       <c r="D31" t="n">
-        <v>0.678768472906404</v>
+        <v>0.713399014778325</v>
       </c>
       <c r="E31" t="n">
-        <v>0.713399014778325</v>
+        <v>0.7193596059113301</v>
       </c>
       <c r="F31" t="n">
-        <v>51.74063255988161</v>
+        <v>41.47772925437926</v>
       </c>
       <c r="G31" t="n">
-        <v>8.376860044756818e-19</v>
+        <v>9.010396346960848e-16</v>
       </c>
     </row>
   </sheetData>
